--- a/results/reliability_eval/Llama-3-8B_P101_sample_30_tokens_0.1_temp_direct_query_scores_08-24-4.xlsx
+++ b/results/reliability_eval/Llama-3-8B_P101_sample_30_tokens_0.1_temp_direct_query_scores_08-24-4.xlsx
@@ -477,31 +477,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.5588552457804756</v>
+        <v>0.6797758766968326</v>
       </c>
       <c r="B2" t="n">
-        <v>0.4948975423003125</v>
+        <v>0.3874022486069838</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5588552457804756</v>
+        <v>0.6797758766968327</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4948975423003125</v>
+        <v>0.3874022486069839</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4329379359367364</v>
+        <v>0.3271856819650937</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4200495396865673</v>
+        <v>0.2091879744736718</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9849171442534097</v>
+        <v>0.9858193277310925</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9789429767911773</v>
+        <v>0.9587616554365931</v>
       </c>
       <c r="I2" t="n">
-        <v>0.451</v>
+        <v>0.272</v>
       </c>
     </row>
   </sheetData>
